--- a/tasks/summarization/ibm-granite-granite-4-2-8b/results.xlsx
+++ b/tasks/summarization/ibm-granite-granite-4-2-8b/results.xlsx
@@ -1,455 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Metrics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Rubric" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sample" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sample Rows" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Samples" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Judges" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Metrics" sheetId="2" r:id="rId2"/>
+    <sheet name="Rubric" sheetId="3" r:id="rId3"/>
+    <sheet name="Sample" sheetId="4" r:id="rId4"/>
+    <sheet name="Sample Rows" sheetId="5" r:id="rId5"/>
+    <sheet name="Samples" sheetId="6" r:id="rId6"/>
+    <sheet name="Judges" sheetId="7" r:id="rId7"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$B$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Metrics'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rubric'!$A$1:$F$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sample'!$A$1:$V$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sample Rows'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Samples'!$A$1:$Q$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Judges'!$A$1:$I$7</definedName>
-  </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-  </fonts>
-  <fills count="3">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
-      </patternFill>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -554,325 +127,325 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>llm_judge_dimension_mean_0_to_5</t>
+          <t>llm_judge_faithfulness_pass_rate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>huggingface_link</t>
+          <t>llm_judge_dimension_mean_0_to_5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://huggingface.co/ibm-granite/granite-4.2-8b</t>
+          <t>4.94</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>model_description</t>
+          <t>huggingface_link</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[](https://huggingface.co/collections/ibm-granite/granite-42-language-models) [](https://huggingface.co/blog/ibm-granite/granite-4-2) [](https://github.com/ibm-granite/granite-4.2-language-models) [](https://www.apache.org/licenses/LICENSE-2.0)</t>
+          <t>https://huggingface.co/ibm-granite/granite-4.2-8b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>model_supported_languages</t>
+          <t>model_description</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>en, de, es, fr, ja, pt, ar, cs, it, ko, nl, zh</t>
+          <t>[](https://huggingface.co/collections/ibm-granite/granite-42-language-models) [](https://huggingface.co/blog/ibm-granite/granite-4-2) [](https://github.com/ibm-granite/granite-4.2-language-models) [](https://www.apache.org/licenses/LICENSE-2.0)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>eval_languages</t>
+          <t>model_supported_languages</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>en, de, es, fr, ja, pt, ar, cs, it, ko, nl, zh</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>assessment</t>
+          <t>eval_languages</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Judges found broadly acceptable outputs with no recurring edge case clearly isolated.</t>
+          <t>en</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inference_time</t>
+          <t>assessment</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16.275s p50 e2e @ c=1 (self_hosted_gpu_colab)</t>
+          <t>Judges found broadly acceptable outputs with no recurring edge case clearly isolated.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>inference_time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NVIDIA A100-SXM4-40GB (34.85 GB)</t>
+          <t>16.275s p50 e2e @ c=1 (self_hosted_gpu_colab)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>vllm_version</t>
+          <t>hardware</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.30.0</t>
+          <t>NVIDIA A100-SXM4-40GB (34.85 GB)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sample_source</t>
+          <t>vllm_version</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>0.30.0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sample_sample_id</t>
+          <t>sample_source</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>c907fe7a8442</t>
+          <t>combined</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sample_sample_count</t>
+          <t>sample_sample_id</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>c907fe7a8442</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sample_jsonl</t>
+          <t>sample_sample_count</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>eval-runs/ibm-granite-granite-4-2-8b/summarization/standard/sample_combined_c907fe7a8442_n2.jsonl</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>sample_jsonl</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>eval-runs/ibm-granite-granite-4-2-8b/summarization/standard/sample_combined_c907fe7a8442_n2.jsonl</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>sample_dataset_count</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Definitions</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>term</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>meaning</t>
+          <t>Definitions</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>llm_judge_dimension_mean_0_to_5</t>
+          <t>term</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>For each sample, each valid LLM judge scores every graded rubric dimension from 0 to 5. The scorer averages judges per dimension, averages those graded dimensions into a sample score, then averages sample scores across the run. Binary gates such as Safety and Faithfulness are not included in this mean.</t>
+          <t>meaning</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>llm_judge_pass_rate</t>
+          <t>llm_judge_dimension_mean_0_to_5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The fraction of samples whose LLM-judge consensus passed: dimension mean is at least 3.0, no graded dimension is 0 or 1, and all binary/ranged gates pass.</t>
+          <t>For each sample, each valid LLM judge scores every graded rubric dimension from 0 to 5. The scorer averages judges per dimension, averages those graded dimensions into a sample score, then averages sample scores across the run. Binary gates such as Safety and Faithfulness are not included in this mean.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>model_supported_languages</t>
+          <t>llm_judge_pass_rate</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Languages claimed by the model card or model metadata. If the model card describes broad support without enumerating every language, the workbook keeps the concise claim, such as 'over 140 languages'.</t>
+          <t>The fraction of samples whose LLM-judge consensus passed: dimension mean is at least 3.0, no graded dimension is 0 or 1, and all binary/ranged gates pass.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>eval_languages</t>
+          <t>model_supported_languages</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Languages covered by this evaluation task or dataset. This is provenance for the run, not the full language capability of the model.</t>
+          <t>Languages claimed by the model card or model metadata. If the model card describes broad support without enumerating every language, the workbook keeps the concise claim, such as 'over 140 languages'.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>inference_time</t>
+          <t>eval_languages</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Performance headline latency. For remote third-party APIs this is the client-observed p50 end-to-end latency from the natural task run, normally at concurrency 1; it includes provider routing, queueing, network, image preprocessing, and model inference. For self-hosted Colab GPU runs it is GPU-only inference latency (no network/provider overhead).</t>
+          <t>Languages covered by this evaluation task or dataset. This is provenance for the run, not the full language capability of the model.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>inference_time</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The hardware the performance timing was measured on. For self-hosted Colab runs this is the exact GPU (name and peak VRAM), pinned across models for comparability. For remote third-party APIs it records that the measurement was client-observed, since the serving hardware is not exposed.</t>
+          <t>Performance headline latency. For remote third-party APIs this is the client-observed p50 end-to-end latency from the natural task run, normally at concurrency 1; it includes provider routing, queueing, network, image preprocessing, and model inference. For self-hosted Colab GPU runs it is GPU-only inference latency (no network/provider overhead).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>vllm_version</t>
+          <t>hardware</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The vLLM engine version that served a self-hosted Colab GPU performance run (the version actually imported on the VM, not merely the one requested). Recorded because the inference engine affects timing, so speed numbers are only comparable within one vLLM version. Absent for remote third-party API benchmarks, which do not use vLLM.</t>
+          <t>The hardware the performance timing was measured on. For self-hosted Colab runs this is the exact GPU (name and peak VRAM), pinned across models for comparability. For remote third-party APIs it records that the measurement was client-observed, since the serving hardware is not exposed.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>token_f1</t>
+          <t>vllm_version</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Token-level F1 between the model output and the reference: treats each as a bag of lowercased word tokens and computes the harmonic mean of precision (fraction of output tokens found in the reference) and recall (fraction of reference tokens found in the output). Ranges 0 to 1; order-insensitive, so it rewards content overlap rather than exact phrasing.</t>
+          <t>The vLLM engine version that served a self-hosted Colab GPU performance run (the version actually imported on the VM, not merely the one requested). Recorded because the inference engine affects timing, so speed numbers are only comparable within one vLLM version. Absent for remote third-party API benchmarks, which do not use vLLM.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>token_f1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Token-level F1 between the model output and the reference: treats each as a bag of lowercased word tokens and computes the harmonic mean of precision (fraction of output tokens found in the reference) and recall (fraction of reference tokens found in the output). Ranges 0 to 1; order-insensitive, so it rewards content overlap rather than exact phrasing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>rouge_l</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>ROUGE-L F1 based on the longest common subsequence (LCS) between output and reference token sequences. Unlike token_f1 it respects word order (the LCS must appear in sequence), so it credits fluent, correctly-ordered overlap. Ranges 0 to 1.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B35"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -995,55 +568,39 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>criterion</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>scale</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
@@ -1070,7 +627,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>misses nearly all key points or is off-topic.</t>
@@ -1098,7 +659,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>captures only a few peripheral points; most salient content is missing.</t>
@@ -1126,7 +691,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>captures some key points but omits several important ones or includes substantial irrelevant detail.</t>
@@ -1154,7 +723,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>captures the main points but with a notable omission or some irrelevant detail.</t>
@@ -1182,7 +755,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>captures most key points with only minor omissions.</t>
@@ -1210,7 +787,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>captures all salient points at an appropriate level of abstraction, closely matching the reference's coverage.</t>
@@ -1238,7 +819,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>disjointed, contradictory, or incoherent.</t>
@@ -1266,7 +851,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>barely organized; frequent jumps between ideas make it hard to follow.</t>
@@ -1294,7 +883,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>loosely organized; some ordering or logic problems.</t>
@@ -1322,7 +915,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>generally organized but with a noticeable ordering or transition problem.</t>
@@ -1350,7 +947,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>mostly well-organized with minor structural issues.</t>
@@ -1378,7 +979,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>clearly and logically organized; ideas flow naturally.</t>
@@ -1406,7 +1011,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>many fabricated or contradictory claims.</t>
@@ -1434,7 +1043,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>multiple fabricated or contradictory claims.</t>
@@ -1462,7 +1075,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>several unsupported claims.</t>
@@ -1490,7 +1107,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>mostly supported but with one clear unsupported claim.</t>
@@ -1518,7 +1139,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>largely faithful with a minor unsupported detail.</t>
@@ -1546,7 +1171,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>every claim is fully supported by the source.</t>
@@ -1574,7 +1203,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>severely ungrammatical or unreadable.</t>
@@ -1602,7 +1235,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>pervasive grammatical/word errors; often hard to read.</t>
@@ -1630,7 +1267,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>frequent grammatical/word errors that hinder reading.</t>
@@ -1658,7 +1299,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>several noticeable grammatical/word errors but still readable.</t>
@@ -1686,7 +1331,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>mostly fluent with minor errors.</t>
@@ -1714,7 +1363,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>fluent, polished, error-free prose.</t>
@@ -1742,7 +1395,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>contains clear hallucinations or fabricated facts.</t>
@@ -1770,7 +1427,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>mostly faithful but with a minor unsupported detail.</t>
@@ -1798,7 +1459,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>fully faithful; every statement is grounded in the source.</t>
@@ -1806,151 +1471,119 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F28"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:V8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="44" customWidth="1" min="14" max="14"/>
-    <col width="60" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="60" customWidth="1" min="21" max="21"/>
-    <col width="19" customWidth="1" min="22" max="22"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>dataset_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>hf_id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>source_hf_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>source_config</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>split</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>source_split</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>revision</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>source_revision</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>sample_count</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sample_id</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>jsonl</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>default_input</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>row_count</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>hf_likes</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>license</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>paper</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>quality_evidence</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>reference_quality</t>
         </is>
@@ -1967,25 +1600,41 @@
           <t>local</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>ccdv/govreport-summarization</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>document</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>4e21184e01ae8017e2c036e180fe5e541fef60a0</t>
@@ -2016,7 +1665,11 @@
           <t>eval-runs/ibm-granite-granite-4-2-8b/summarization/standard/sample_local_1aab8ec6466f_n1_s1234.jsonl</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
@@ -2032,7 +1685,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>GovReport (Huang et al. 2021, arXiv:2104.02112) is a standard long-document summarization benchmark widely used in efficient-attention / long-context summarization papers and leaderboards. 973-row test split; report/summary fields with high-quality human reference summaries.</t>
@@ -2055,25 +1712,41 @@
           <t>local</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>FiscalNote/billsum</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>3d8510441c06a3d9dfb32eb0d7f80151730bcc4f</t>
@@ -2104,7 +1777,11 @@
           <t>eval-runs/ibm-granite-granite-4-2-8b/summarization/standard/sample_local_d2d408dbbd7c_n1_s1234.jsonl</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
@@ -2120,7 +1797,11 @@
           <t>cc0-1.0</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>BillSum (Kornilova &amp; Eidelman, ACL 2019 New Frontiers in Summarization, arXiv:1910.00523) is a well-established US-legislation summarization benchmark with human-written reference summaries; 3269-row test split.</t>
@@ -2177,31 +1858,19 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V8"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>dataset_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>row_index</t>
         </is>
@@ -2232,121 +1901,89 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="33" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="17" customWidth="1" min="17" max="17"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>dataset</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>reference</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>output</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>has_image</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>overall_pass</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>llm_judge_dimension_mean_0_to_5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>safety_pass</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>faithfulness_pass</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>dim_Coherence</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>dim_Consistency</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>dim_Fluency</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>dim_Relevance</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>gate_Faithfulness</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>metric_rouge_l</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>metric_token_f1</t>
         </is>
@@ -2401,15 +2038,19 @@
           <t>4.88</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -2424,20 +2065,15 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
-        <is>
-          <t>0.157</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
         <is>
           <t>0.3916</t>
         </is>
@@ -2556,7 +2192,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Community Gardening and Nutrition Act of 2014 - Amends the Domestic Volunteer Service Act of 1973 to require the Director of the Corporation for National and Community Service to establish a Community Garden Pilot Program under the Volunteers in Service to America (VISTA) program. Requires the Program to address the health and nutrition of individuals in low-income and underserved communities through activities that include:  creating new community gardens and supporting and expanding existing community gardens; recruiting local community members to actively engage in community gardens and gardening projects; transforming vacant places into community garden plots; increasing community members' access to healthy foods and local foods while also encouraging them to stay active; expanding anti-poverty efforts by teaching basic nutrition and self-reliance through community gardening; and developing initiatives that increase the community's access to healthy, locally grown foods.  Requires the Director to carry out at least 40 projects under the Program. Requires the Director to give priority to: (1) volunteers with experience in health, nutrition, and gardening; (2) projects located in varied geographic regions; and (3) selecting a balance of urban and rural projects.  </t>
+          <t>Community Gardening and Nutrition Act of 2014 - Amends the Domestic Volunteer Service Act of 1973 to require the Director of the Corporation for National and Community Service to establish a Community Garden Pilot Program under the Volunteers in Service to America (VISTA) program. Requires the Program to address the health and nutrition of individuals in low-income and underserved communities through activities that include:  creating new community gardens and supporting and expanding existing community gardens; recruiting local community members to actively engage in community gardens and gardening projects; transforming vacant places into community garden plots; increasing community members' access to healthy foods and local foods while also encouraging them to stay active; expanding anti-poverty efforts by teaching basic nutrition and self-reliance through community gardening; and developing initiatives that increase the community's access to healthy, locally grown foods.  Requires the Director to carry out at least 40 projects under the Program. Requires the Director to give priority to: (1) volunteers with experience in health, nutrition, and gardening; (2) projects located in varied geographic regions; and (3) selecting a balance of urban and rural projects.  </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2595,10 +2231,14 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2618,93 +2258,69 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.1518</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.1518</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
           <t>0.33</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q3"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>sample_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>judge</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>parsed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>reasoning</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Coherence</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Consistency</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Faithfulness</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Fluency</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Relevance</t>
         </is>
@@ -2820,12 +2436,36 @@
           <t>False</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2937,15 +2577,37 @@
           <t>False</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I7"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tasks/summarization/ibm-granite-granite-4-2-8b/results.xlsx
+++ b/tasks/summarization/ibm-granite-granite-4-2-8b/results.xlsx
@@ -332,7 +332,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>For each sample, each valid LLM judge scores every graded rubric dimension from 0 to 5. The scorer averages judges per dimension, averages those graded dimensions into a sample score, then averages sample scores across the run. Binary gates such as Safety and Faithfulness are not included in this mean.</t>
+          <t>For each sample, each valid LLM judge scores every graded rubric dimension from 0 to 5. The scorer averages judges per dimension, averages those graded dimensions into a sample score, then averages sample scores across the run. Gate scores are not included in this mean.</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>For each sample, each valid LLM judge scores every graded rubric dimension from 0 to 5. The scorer averages judges per dimension, averages those graded dimensions into a sample score, then averages sample scores across the run. Binary gates such as Safety and Faithfulness are not included in this mean.</t>
+          <t>For each sample, each valid LLM judge scores every graded rubric dimension from 0 to 5. The scorer averages judges per dimension, averages those graded dimensions into a sample score, then averages sample scores across the run. Gate scores are not included in this mean.</t>
         </is>
       </c>
     </row>

--- a/tasks/summarization/ibm-granite-granite-4-2-8b/results.xlsx
+++ b/tasks/summarization/ibm-granite-granite-4-2-8b/results.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>evalplan-8bc5c6c7e586fd90f9f0</t>
+          <t>evalplan-e88c5328000e64975571</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8bc5c6c7e586fd90f9f0c69cd1f668399e261d99b622086f02faa74249003a60</t>
+          <t>e88c5328000e649755715be8cd18af620d8e5744025698f32d335978f32c6fd5</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.5218</t>
+          <t>0.5524</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.2825</t>
+          <t>0.2897</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.5218</t>
+          <t>0.5524</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.2825</t>
+          <t>0.2897</t>
         </is>
       </c>
     </row>
@@ -2405,10 +2405,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>U.S.–Iran relations have been largely adversarial since Iran’s 1979 Islamic Revolution. After 2002, U.S. policy prioritized constraining Iran’s nuclear program, preventing the purchase of new conventional weapons and ballistic missiles, and addressing Iran’s support for militant armed groups in the Middle East. In May 2018 the Trump administration withdrew from the 2015 Joint Comprehensive Plan of Action (JCPOA), describing it as insufficient to address U.S. concerns and capable of allowing Iran to develop a nuclear weapon. The administration applied “maximum pressure,” imposing expanded sanctions and ending most Iran‑related waivers under the Iran Freedom and Counter‑Proliferation Act to compel Iran to renegotiate the JCPOA and deny it revenue for strategic capabilities. Officials deny the goal is to provoke economic unrest in Iran.
-Key 2019–2020 developments heightened tensions: the administration designated the Islamic Revolutionary Guard Corps (IRGC) as a Foreign Terrorist Organization; ended a U.S. oil‑purchase waiver for all countries; accelerated deployment of a carrier strike group and bomber task force to the Persian Gulf; notified Congress of emergency defense sales exceeding $8 billion to Saudi Arabia and the United Arab Emirates; and publicly warned that any IRGC gunboat harassment of U.S. ships would be met with a shoot‑down. Iran responded with attacks on commercial tankers in the Gulf of Oman and elsewhere, ballistic‑missile testing, and support for regional militias (e.g., Hezbollah, Houthis, Kataʾib Hezbollah). U.S. officials attributed several attacks—including rocket fire in Baghdad, attacks on Saudi oil infrastructure, and tanker seizures—to Iran or its proxies, while Iran denied responsibility for some incidents.
-In January 2020 the United States killed IRGC‑Quds Force commander Qasem Soleimani with a drone strike; Iran retaliated with ballistic‑missile strikes on Iraqi bases. Both sides avoided large‑scale military retaliation, but U.S. forces increased in the region—adding roughly 14,000 personnel to an existing base of over 60,000—deploying Patriot and THAAD systems, reinforcing naval patrols (e.g., the International Maritime Security Construct), and pursuing new sanctions (e.g., designating Iran’s central bank and sovereign wealth fund as terrorism‑supporting entities). Iran continued to exceed JCPOA limits on heavy water, low‑enriched uranium, centrifuge numbers, and related research; it announced steps toward lifting centrifuge restrictions and resumed some nuclear activities.
-Throughout 2019‑2020 Congress passed language in FY2020 appropriations and the NDAA stating that nothing authorizes the use of military force against Iran, while the administration asserted broad constitutional and existing authority to act without congressional approval. After the Soleimani strike, bipartisan congressional resolutions urged termination of U.S. hostilities with Iran; the president vetoed one such resolution. The report outlines potential U.S. military options—including air and missile strikes, cyber and electronic actions, naval blockades, and limited proxy targeting—while noting risks of escalation, cost, and political consequences. It emphasizes that the administration’s core objective is systemic change in Iran’s hostile and destabilizing actions, including blocking a nuclear weapon and curbing terrorism, and that additional deployments aim to deter further Iranian provocations rather than signal an imminent offensive. The summary captures the evolving pattern of sanctions, military posture adjustments, regional proxy actions, diplomatic dead‑ends, and congressional war‑powers debates without adding information not present in the document.</t>
+          <t>U.S.–Iran relations have been largely adversarial since the 1979 Islamic Revolution, with U.S. officials repeatedly identifying Iran’s support for militant armed factions in the Middle East as a significant threat to U.S. interests and allies. After 2002, constraining Iran’s nuclear program became the priority, followed by efforts to block Iran’s purchase of new conventional weapons and development of ballistic missiles. In May 2018 the Trump administration withdrew from the 2015 Joint Comprehensive Plan of Action (JCPOA), asserting the agreement did not address U.S. concerns and could not permanently preclude a nuclear weapon. The administration described its policy as “maximum pressure,” using sanctions and economic measures to (1) compel Iran to renegotiate the JCPOA to address U.S. concerns and (2) deny Iran revenue needed to develop strategic capabilities or intervene regionally. Officials denied that the policy aims to provoke economic unrest in Iran.
+Key 2019 developments heightened tensions: on 8 April the administration designated the Islamic Revolutionary Guard Corps (IRGC) as a Foreign Terrorist Organization, alleging it provides financial, technical and weapons support to groups including Hezbollah, Hamas, Kataʾib Hezbollah, al‑Ashtar Brigades and others; on 2 May a sanctions exception for foreign purchases of Iranian oil was ended, aiming to drive Iran’s oil exports to zero; on 5 May National Security Adviser John Bolton announced acceleration of deployment of the USS Abraham Lincoln carrier strike group and a bomber task force to the Persian Gulf; on 24 May the administration notified Congress of emergency foreign military sales and export licenses worth over $8 billion, citing the need to deter Iranian adventurism. Iran responded by attacking commercial shipping—four tankers were damaged in May 2019 (two Saudi, one Emirati, one Norwegian) and two Saudi tankers were hit in June 2019—while the U.S. attributed the attacks to the IRGC. Additional Iranian actions included rocket fire into Baghdad’s Green Zone, attacks on Saudi pipeline infrastructure, a car bombing in Afghanistan, and the downing of a U.S. RQ‑4 Global Hawk drone near the Strait of Hormuz. The U.S. also seized Iranian‑flagged tankers in the Gulf (Grace I and Stena Impero) and responded with diplomatic pressure and naval deployments.
+In September 2019 Iran launched cruise‑missile and unmanned‑aircraft strikes on Saudi oil facilities at Khurais and Abqaiq, causing a sharp drop in Saudi production; the U.S. assessed the attacks as Iranian in origin despite Houthi claims. The Trump administration imposed further sanctions, including blocking U.S. property of Iran’s Supreme Leader and top IRGC officials, designating Iran’s central bank and national development fund as terrorism‑supporting entities, and offering up to $15 million for assistance in disrupting IRGC financial operations. Executive Orders 13871 (May 8 2019) and 13876 (June 24 2019) targeted Iran’s metal‑sector transactions and senior officials, respectively.
+Iran rejected renegotiation of the JCPOA, stopped transferring low‑enriched uranium and heavy water, and began exceeding JCPOA limits on centrifuges, heavy water stockpiles and LEU concentrations, as verified by the IAEA. Iran announced a “fifth and final step” to remove centrifuge limits and said it would resume JCPOA commitments only if sanctions were lifted. In December 2019 Iran supplied short‑range missiles to Iraqi allies and launched indirect fire attacks; the U.S. retaliated with airstrikes on Kataʾib Hezbollah facilities. On 3 January 2020 a U.S. drone strike killed IRGC‑QF commander Qasem Soleimani and PMF leader Abu Mahdi al‑Muhandis; Iran responded with ballistic‑missile strikes on Iraqi bases (Operation Martyr Soleimani). Tensions continued with IRGC boarding of a Hong Kong‑flagged tanker, harassing approaches to U.S. naval vessels, and Iran’s launch of a military satellite.
+The U.S. increased its Gulf military presence, adding roughly 14,000 personnel to a baseline of over 60,000, deploying Patriot and THAAD systems, and establishing the International Maritime Security Construct (IMSC/Operation Sentinel) to protect shipping. Congress passed NDAA provisions stating that nothing authorizes the use of military force against Iran, while the administration asserted broad presidential authority to act without congressional approval. Legislative responses included the No War Against Iran Act (House) and Senate resolutions directing termination of hostilities, which were vetoed by the president. Ongoing debates focus on the need for congressional authorization, the legality of preventive or retaliatory strikes, potential costs, and the role of regional allies. The report outlines several possible military options—targeted strikes, proxy actions, naval blockades, and limited force use—while noting risks of escalation, cost, and impact on diplomatic prospects.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2458,12 +2459,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.1829</t>
+          <t>0.1812</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.4832</t>
+          <t>0.4793</t>
         </is>
       </c>
     </row>
@@ -2585,10 +2586,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The Community Gardening and Nutrition Act of 2014 establishes a Community Garden Pilot Program under the Domestic Volunteer Service Act of 1973. The Act finds that community gardens improve quality of life, encourage self‑reliance, produce nutritious food, reduce food costs, provide recreation, social interaction, exercise, education, and economic development; they also help clean up abandoned vacant lots and supply fresh produce to food pantries, cooperatives, and homeless individuals. Supporting evidence includes reports indicating that meeting daily fruit and vegetable recommendations could prevent nearly 130,000 deaths and save $17 billion in medical costs, findings on healthy dietary patterns from the Department of Health and Human Services, and research showing community gardens promote healthy behaviors, improve children’s dietary intake, and reduce childhood obesity.
-The Act amends section 103(a) of the Domestic Volunteer Service Act to add paragraph (14), which directs initiatives to address health and nutrition in low‑income and underserved communities by creating new community gardens, supporting existing gardens, recruiting local volunteers, transforming vacant places into garden plots, increasing access to healthy and local foods while encouraging physical activity, expanding anti‑poverty efforts through nutrition and self‑reliance education, and improving broad community access to locally grown healthy foods.
-Part A of title I of the Act is amended to add section 110, the Community Garden Pilot Program. The Director shall establish the program to carry out the work described in paragraph (14) and must conduct at least 40 projects. Priority will be given to volunteers with health, nutrition, and gardening experience; projects in varied geographic regions; and a balance of urban and rural sites. Authorization amends section 501(a) to provide $4,000,000 for fiscal year 2014 for the pilot program, to remain available until expended. A clerical amendment adds “Sec. 110. Community Garden Pilot Program” to the table of contents.
-Within 90 days after the pilot program’s completion, the Assistant Director under the National and Community Service Act of 1990 must submit a report to Congress describing the projects and volunteer placements, presenting results and analysis of completed projects, and offering recommendations for continuing the program.</t>
+          <t>The Community Gardening and Nutrition Act of 2014 establishes a Community Garden Pilot Program under the Domestic Volunteer Service Act of 1973. The program aims to address health and nutrition in low‑income and underserved communities by creating new community gardens, supporting existing gardens, recruiting local volunteers, transforming vacant lots into garden plots, increasing access to healthy and local foods, encouraging physical activity, teaching basic nutrition and self‑reliance, and expanding access to locally grown foods. The Director of the relevant agency must establish at least 40 projects and prioritize volunteers with health, nutrition, and gardening experience; projects should be spread across varied geographic regions and balance urban and rural locations. The legislation amends the Domestic Volunteer Service Act to add paragraph (14) to section 103(a) describing these garden‑related initiatives, adds a new section 110 (Community Garden Pilot Program) that outlines the program’s purpose, priority criteria, and the requirement to carry out no fewer than 40 projects, redesignates a paragraph in section 501(a) and inserts a new paragraph authorizing $4,000,000 for fiscal year 2014 for the program, and updates the table of contents. Within 90 days after the pilot program’s completion, the Assistant Director under the National and Community Service Act of 1990 must submit a report to Congress describing the projects and volunteer placements, presenting results and analysis of completed projects, and offering recommendations for continuing the program.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2638,12 +2636,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.3822</t>
+          <t>0.3981</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.5603</t>
+          <t>0.6256</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2736,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Relevance: The summary captures all salient points from the reference, including the U.S. withdrawal from the JCPOA, the 'maximum pressure' campaign, key escalations in 2019–2020, the Soleimani strike, Iranian responses, military deployments, congressional actions, and diplomatic stalemate, while maintaining appropriate abstraction and focus. | Coherence: The summary is well-structured, with a clear chronological and thematic flow that connects U.S. policy shifts, Iranian responses, military actions, and diplomatic developments. Transitions between events and policy implications are logical and cohesive. | Consistency: The summary accurately reflects all key events, policies, and actions described in the reference text without introducing unsupported claims or contradictions. Every major point, including the U.S. withdrawal from the JCPOA, the 'maximum pressure' campaign, IRGC designations, attacks on tankers, the Soleimani strike, Iranian nuclear escalations, military deployments, and congressional actions, is directly supported by the source. | Fluency: The response is grammatically correct, clear, and free of errors, with smooth sentence structure and precise word choice throughout. | Faithfulness: The summary accurately reflects all key events, policies, and actions described in the source document, including the U.S. withdrawal from the JCPOA, maximum pressure campaign, designations, military deployments, attacks, retaliations, and congressional responses, with no unsupported claims.</t>
+          <t>Relevance: The summary captures all salient points from the reference, including the U.S. withdrawal from the JCPOA, the 'maximum pressure' campaign, Iran's retaliatory actions, the killing of Soleimani, subsequent hostilities, military deployments, diplomatic efforts, and congressional responses, matching the reference's scope and emphasis. | Coherence: The summary is well-structured with a clear chronological and thematic flow, connecting U.S.-Iran tensions, key events, policy responses, and military developments in a logical sequence. | Consistency: All claims in the summary are directly supported by the source document, with no hallucinations or contradictions; key events, dates, and policy positions are accurately represented. | Fluency: The response is grammatically correct, clear, and free of errors, with smooth sentence structure and precise word choice throughout. | Faithfulness: The summary accurately reflects all key events, policies, and actions described in the source document, with no unsupported claims or hallucinations.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2785,7 +2783,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Relevance: The summary accurately captures the key points of the reference, including the adversarial U.S.-Iran relations, the 2018 withdrawal from the JCPOA, the 'maximum pressure' campaign, and the escalation of tensions in 2019-2020, such as the Soleimani strike and Iran's nuclear activities. It omits only minor details like specific sanctions or congressional actions. | Coherence: The summary is well-structured, logically organized, and flows naturally, with clear transitions between key events and policies. It presents a unified narrative of U.S.-Iran tensions, from historical context to recent developments, without contradictions or disjointed ideas. | Consistency: The summary accurately reflects the source document, citing specific events (e.g., IRGC designation, Soleimani strike, JCPOA violations) and policies (e.g., 'maximum pressure') without introducing unsupported claims or contradictions. | Fluency: The text is well-structured, grammatically correct, and free of errors, with clear and precise language throughout. It effectively conveys complex information without ambiguity. | Faithfulness: The summary accurately reflects the source document's details on U.S.-Iran tensions, including the 2018 JCPOA withdrawal, 'maximum pressure' policy, key 2019-2020 events (e.g., Soleimani strike, missile attacks), and Iran's nuclear program violations. No fabricated facts or unsupported claims are present.</t>
+          <t>Relevance: The summary captures key points such as the adversarial U.S.-Iran relations, the 2018 JCPOA withdrawal, 'maximum pressure' policy, and major 2019-2020 escalations (e.g., Soleimani strike, Saudi oil attacks). It omits minor details (e.g., specific sanctions dates) but aligns closely with the reference's coverage. | Coherence: The summary is well-structured, with a clear chronological and thematic progression from historical context to recent events, and logical transitions between key developments. Ideas flow naturally, making it easy to follow the escalation of tensions and responses from both sides. | Consistency: The summary accurately reflects the source document, citing specific events (e.g., IRGC designation, tanker attacks, Soleimani strike) and policies (e.g., 'maximum pressure,' JCPOA withdrawal) without contradictions or unsupported claims. | Fluency: The text is well-structured, grammatically correct, and free of errors, with clear and precise language throughout. It demonstrates polished, error-free prose. | Faithfulness: The summary accurately reflects the source document's details on U.S.-Iran tensions, including the 2018 JCPOA withdrawal, 'maximum pressure' policy, key 2019 events (e.g., IRGC designation, tanker attacks, Soleimani strike), and Iran's nuclear program violations. No fabricated facts or hallucinations are present.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2855,7 +2853,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Relevance: The summary captures all key points from the source, including the purpose, findings, program establishment, funding, and reporting requirement, with high fidelity to the original text. | Coherence: The summary is logically structured, following the order of the original text with clear transitions between sections and ideas. Each part flows naturally to the next, maintaining a unified focus on the Act's provisions. | Consistency: All claims in the summary are directly supported by the source document, with no hallucinations or contradictions. | Fluency: The response is grammatically correct, clear, and free of errors, with smooth sentence structure and precise word choice. | Faithfulness: The summary accurately reflects all key elements from the source document, including the purpose, findings, amendments, program details, funding, and reporting requirement, with no hallucinations or unsupported claims.</t>
+          <t>Relevance: The summary captures all key elements from the reference, including the establishment of the Community Garden Pilot Program, its goals, required activities, project and volunteer priorities, funding authorization, and reporting requirement, closely aligning with the salient points. | Coherence: The summary is logically structured, with a clear sequence that follows the original legislation's organization, connecting each component smoothly and coherently. | Consistency: Every claim in the summary is directly supported by the source document, with no hallucinations or contradictions; all details about the program's purpose, requirements, funding, and reporting are accurately reflected. | Fluency: The response is grammatically correct, clear, and free of errors, with smooth sentence structure and precise word choice. | Faithfulness: The summary accurately reflects all key elements of the source document, including the program's purpose, required activities, project minimum, priority criteria, funding authorization, and reporting requirement, with no hallucinations or unsupported details.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2902,7 +2900,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Relevance: The summary captures all key points from the reference, including the purpose, findings, program details, and reporting requirements, with no notable omissions or irrelevant details. | Coherence: The summary logically organizes the Act's structure, starting with the title and findings, then detailing the pilot program's purpose, establishment, and requirements, followed by reporting obligations. Ideas flow naturally with clear transitions between sections. | Consistency: The summary accurately reflects all findings, amendments, and program details from the source document without any unsupported claims or contradictions. Every claim is directly supported by the text, including the benefits of community gardens, the pilot program's requirements, and reporting obligations. | Fluency: The text is well-structured, grammatically correct, and free of errors, with clear and polished prose throughout. | Faithfulness: The summary accurately reflects all key findings, program details, and requirements from the source document, including the $4M funding, 40-project minimum, and priority criteria. No unsupported or fabricated details are present.</t>
+          <t>Relevance: The summary accurately captures all key points of the reference, including the program's purpose, requirements, priorities, and reporting obligations, without omissions or irrelevant details. | Coherence: The summary logically organizes the Act's key components—purpose, program establishment, funding, and reporting—with clear transitions between sections. Ideas flow naturally, supporting the unified theme of promoting community gardens for health and nutrition. | Consistency: The summary accurately reflects all key details from the source, including the program's purpose, requirements (e.g., 40 projects), priority criteria, funding, and reporting obligations, with no unsupported claims or contradictions. | Fluency: The text is well-structured, grammatically correct, and free of errors, with clear and polished prose throughout. It adheres to formal legislative language without hindering readability. | Faithfulness: The summary accurately reflects all key details from the source, including the program's purpose, requirements (e.g., 40 projects), funding, and reporting obligations, with no fabricated or unsupported claims.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/tasks/summarization/ibm-granite-granite-4-2-8b/results.xlsx
+++ b/tasks/summarization/ibm-granite-granite-4-2-8b/results.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Judges" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$B$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$B$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Metrics'!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rubric'!$A$1:$F$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sample'!$A$1:$V$8</definedName>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -715,176 +715,356 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15.081s p50 e2e @ c=1 (self_hosted_gpu_colab)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sample_source</t>
+          <t>hardware</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>NVIDIA A100-SXM4-40GB (34.46 GB)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sample_sample_id</t>
+          <t>vllm_version</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>c907fe7a8442</t>
+          <t>0.31.0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sample_sample_count</t>
+          <t>performance_comparability</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>comparable</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sample_jsonl</t>
+          <t>performance_comparability_reason</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>eval-runs/ibm-granite-granite-4-2-8b/summarization/standard/sample_combined_c907fe7a8442_n2.jsonl</t>
+          <t>Workload, request counts, runtime, and measurement scope are complete.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sample_dataset_count</t>
+          <t>performance_comparability_key</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
+          <t>1d9f7dc05dfe31d00c3f061630858ba512bfc8003ecd72a085097cb0599fee55</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>performance_workload_sha256</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>bbedeabcb998219882636db76b900b9aa5c73345c51a6f731e8336af2e248361</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Definitions</t>
+          <t>performance_measurement</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2 frozen rows; 100 requests/sweep at [1, 4, 8, 16]; 400/400 measured requests succeeded; 0/0 warmups succeeded</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>term</t>
+          <t>ttft_availability</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>meaning</t>
+          <t>N/A — Offline vLLM does not expose reliable first-token timing.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>llm_judge_dimension_mean_0_to_5</t>
+          <t>gpu_memory_availability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>For each sample, each valid LLM judge scores every graded rubric dimension from 0 to 5. The scorer averages judges per dimension, averages those graded dimensions into a sample score, then averages sample scores across the run. Gate scores are not included in this mean.</t>
+          <t>available</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>llm_judge_pass_rate</t>
+          <t>sample_source</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The fraction of samples whose LLM-judge consensus passed: dimension mean is at least 3.0, no graded dimension is 0 or 1, and all binary/ranged gates pass.</t>
+          <t>combined</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>model_supported_languages</t>
+          <t>sample_sample_id</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Languages claimed by the model card or model metadata. If the model card describes broad support without enumerating every language, the workbook keeps the concise claim, such as 'over 140 languages'.</t>
+          <t>c907fe7a8442</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>eval_languages</t>
+          <t>sample_sample_count</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Languages covered by this evaluation task or dataset. This is provenance for the run, not the full language capability of the model.</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>inference_time</t>
+          <t>sample_jsonl</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Performance headline latency. For remote third-party APIs this is the client-observed p50 end-to-end latency from the natural task run, normally at concurrency 1; it includes provider routing, queueing, network, image preprocessing, and model inference. For self-hosted Colab GPU runs it is GPU-only inference latency (no network/provider overhead).</t>
+          <t>eval-runs/ibm-granite-granite-4-2-8b/summarization/standard/sample_combined_c907fe7a8442_n2.jsonl</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>sample_dataset_count</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>llm_judge_dimension_mean_0_to_5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>For each sample, each valid LLM judge scores every graded rubric dimension from 0 to 5. The scorer averages judges per dimension, averages those graded dimensions into a sample score, then averages sample scores across the run. Gate scores are not included in this mean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>llm_judge_pass_rate</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>The fraction of samples whose LLM-judge consensus passed: dimension mean is at least 3.0, no graded dimension is 0 or 1, and all binary/ranged gates pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>model_supported_languages</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Languages claimed by the model card or model metadata. If the model card describes broad support without enumerating every language, the workbook keeps the concise claim, such as 'over 140 languages'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>eval_languages</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Languages covered by this evaluation task or dataset. This is provenance for the run, not the full language capability of the model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>inference_time</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Performance headline latency. For remote third-party APIs this is the client-observed p50 end-to-end latency from the natural task run, normally at concurrency 1; it includes provider routing, queueing, network, image preprocessing, and model inference. For self-hosted Colab GPU runs it is GPU-only inference latency (no network/provider overhead).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>hardware</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>The hardware the performance timing was measured on. For self-hosted Colab runs this is the exact GPU (name and peak VRAM), pinned across models for comparability. For remote third-party APIs it records that the measurement was client-observed, since the serving hardware is not exposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>vllm_version</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>The vLLM engine version that served a self-hosted Colab GPU performance run (the version actually imported on the VM, not merely the one requested). Recorded because the inference engine affects timing, so speed numbers are only comparable within one vLLM version. Absent for remote third-party API benchmarks, which do not use vLLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>performance_comparability</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Whether the performance artifact passed its frozen-workload, request-count, hardware, and runtime contract. Only rows with the same comparability key are directly comparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>performance_comparability_key</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>A SHA-256 grouping key over shared benchmark conditions. Different models may be compared only when this key matches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>performance_workload_sha256</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SHA-256 of the frozen prompt-row identities, prompt content hashes, system prompt, and generation limits used for the benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>performance_measurement</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>The actual frozen dataset-row count, measured requests at each concurrency level, successful request count, and completed warmups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>token_f1</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Token-level F1 between the model output and the reference: treats each as a bag of lowercased word tokens and computes the harmonic mean of precision (fraction of output tokens found in the reference) and recall (fraction of reference tokens found in the output). Ranges 0 to 1; order-insensitive, so it rewards content overlap rather than exact phrasing.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>rouge_l</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>ROUGE-L F1 based on the longest common subsequence (LCS) between output and reference token sequences. Unlike token_f1 it respects word order (the LCS must appear in sequence), so it credits fluent, correctly-ordered overlap. Ranges 0 to 1.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B38"/>
+  <autoFilter ref="A1:B53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/tasks/summarization/ibm-granite-granite-4-2-8b/results.xlsx
+++ b/tasks/summarization/ibm-granite-granite-4-2-8b/results.xlsx
@@ -439,7 +439,7 @@
   <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -638,7 +638,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>llm_judge_dimension_mean_0_to_5</t>
+          <t>LLM Judge Mean Factor Score (0–5)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>llm_judge_dimension_mean_0_to_5</t>
+          <t>LLM Judge Mean Factor Score (0–5)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1078,7 +1078,7 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1133,7 +1133,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>llm_judge_dimension_mean_0_to_5</t>
+          <t>LLM Judge Mean Factor Score (0–5)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1165,7 +1165,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>llm_judge_dimension_mean_0_to_5</t>
+          <t>LLM Judge Mean Factor Score (0–5)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2469,7 +2469,7 @@
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>llm_judge_dimension_mean_0_to_5</t>
+          <t>LLM Judge Mean Factor Score (0–5)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
